--- a/data/trans_orig/P16A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>37212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72382</t>
+          <t>72320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430157</t>
+          <t>429913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453089</t>
+          <t>452262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269837</t>
+          <t>269468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289699</t>
+          <t>288578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708075</t>
+          <t>708137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738056</t>
+          <t>737105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66949</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328898</t>
+          <t>330751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350263</t>
+          <t>350668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332132</t>
+          <t>331165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352732</t>
+          <t>352357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671850</t>
+          <t>669754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699246</t>
+          <t>698353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31750</t>
+          <t>30190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>56554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>28063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77626</t>
+          <t>75503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485245</t>
+          <t>485835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510639</t>
+          <t>512199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141332</t>
+          <t>139719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157697</t>
+          <t>157181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632545</t>
+          <t>634668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664699</t>
+          <t>665030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70294</t>
+          <t>69739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104741</t>
+          <t>104425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>36923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>63853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115885</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160697</t>
+          <t>160656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133593</t>
+          <t>1133909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1168040</t>
+          <t>1168595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649738</t>
+          <t>650432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>676269</t>
+          <t>677362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1791923</t>
+          <t>1791964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1836735</t>
+          <t>1837465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20767</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45233</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74455</t>
+          <t>72708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314005</t>
+          <t>314096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332641</t>
+          <t>332136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>523519</t>
+          <t>524132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547985</t>
+          <t>546992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843834</t>
+          <t>845581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>873675</t>
+          <t>875859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>79730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64323</t>
+          <t>62062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271630</t>
+          <t>271002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287796</t>
+          <t>287655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1169017</t>
+          <t>1169030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1198291</t>
+          <t>1198623</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1449335</t>
+          <t>1448842</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1482637</t>
+          <t>1484898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199591</t>
+          <t>196942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257786</t>
+          <t>255933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192203</t>
+          <t>191521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250444</t>
+          <t>246866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>403867</t>
+          <t>400404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485389</t>
+          <t>482527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3011386</t>
+          <t>3013239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3069581</t>
+          <t>3072230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3127680</t>
+          <t>3131258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3185921</t>
+          <t>3186603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6161907</t>
+          <t>6164769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6243429</t>
+          <t>6246892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66750</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37990</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60562</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96047</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370461</t>
+          <t>372632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401205</t>
+          <t>400608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276464</t>
+          <t>276482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296896</t>
+          <t>296828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>655618</t>
+          <t>655589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>691103</t>
+          <t>692052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44550</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79900</t>
+          <t>79185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372468</t>
+          <t>373572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396639</t>
+          <t>397859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>292276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314357</t>
+          <t>313807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>672433</t>
+          <t>673148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705182</t>
+          <t>706579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72217</t>
+          <t>69724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57750</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93312</t>
+          <t>93049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554121</t>
+          <t>556614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585220</t>
+          <t>585773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228717</t>
+          <t>226509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245321</t>
+          <t>245549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790964</t>
+          <t>791227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>826526</t>
+          <t>825435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93146</t>
+          <t>95033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137578</t>
+          <t>138764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>62548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98815</t>
+          <t>96975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167777</t>
+          <t>167718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226049</t>
+          <t>222799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1019737</t>
+          <t>1018551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1064169</t>
+          <t>1062282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667842</t>
+          <t>669682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>703914</t>
+          <t>704109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1697924</t>
+          <t>1701174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1756196</t>
+          <t>1756255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34739</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>68856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>83276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>119750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451510</t>
+          <t>449652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475857</t>
+          <t>475651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>687707</t>
+          <t>688386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716423</t>
+          <t>716046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145367</t>
+          <t>1148089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1185851</t>
+          <t>1184563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68436</t>
+          <t>67021</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106055</t>
+          <t>103102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90483</t>
+          <t>92697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132021</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227644</t>
+          <t>226221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247769</t>
+          <t>248001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>999201</t>
+          <t>1002154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036820</t>
+          <t>1038235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1239077</t>
+          <t>1234940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1280615</t>
+          <t>1278401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>286188</t>
+          <t>285970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>355713</t>
+          <t>358663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261614</t>
+          <t>265768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>328685</t>
+          <t>330987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>570034</t>
+          <t>571536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>666341</t>
+          <t>670424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3058606</t>
+          <t>3055656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3128131</t>
+          <t>3128349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3208179</t>
+          <t>3205877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3275250</t>
+          <t>3271096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6284842</t>
+          <t>6280759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6381149</t>
+          <t>6379647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52147</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>35096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>45936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>77147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376945</t>
+          <t>380513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403644</t>
+          <t>404330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>312607</t>
+          <t>311959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331876</t>
+          <t>331671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697960</t>
+          <t>699000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729969</t>
+          <t>730211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79792</t>
+          <t>75797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336231</t>
+          <t>336651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358661</t>
+          <t>358560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326067</t>
+          <t>325465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349844</t>
+          <t>348286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669708</t>
+          <t>673703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701769</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>59355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47288</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>77162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462949</t>
+          <t>462559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489066</t>
+          <t>487819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>140233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156782</t>
+          <t>156783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611710</t>
+          <t>610874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640748</t>
+          <t>641283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73822</t>
+          <t>74134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110198</t>
+          <t>112492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78913</t>
+          <t>82132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131605</t>
+          <t>130173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182430</t>
+          <t>178671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1039440</t>
+          <t>1037146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1075816</t>
+          <t>1075504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>746963</t>
+          <t>743744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>775892</t>
+          <t>775133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1793084</t>
+          <t>1796843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1843909</t>
+          <t>1845341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31689</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,82 +7390,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>60314</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>46551</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>77988</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>102971</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>86404</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>124986</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60314</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>46346</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76848</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>102971</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>84985</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>124643</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>563580</t>
+          <t>563481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>589017</t>
+          <t>589605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,82 +7503,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>677930</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>660256</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>691693</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1255979</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1233964</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1272546</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>92,42%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>90,8%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>677930</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>661396</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>691898</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,59%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1197</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1255979</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1234307</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1273965</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,42%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79122</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120776</t>
+          <t>121110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96094</t>
+          <t>96512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139302</t>
+          <t>140425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259369</t>
+          <t>258733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275105</t>
+          <t>275871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>961249</t>
+          <t>960915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1002903</t>
+          <t>1002270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1229868</t>
+          <t>1228745</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1273076</t>
+          <t>1272658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230994</t>
+          <t>231197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>297200</t>
+          <t>294223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263670</t>
+          <t>264529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329986</t>
+          <t>327780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>506717</t>
+          <t>511099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>599253</t>
+          <t>604067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3088522</t>
+          <t>3091499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3154728</t>
+          <t>3154525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3201610</t>
+          <t>3203816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3267926</t>
+          <t>3267067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6318065</t>
+          <t>6313251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6410601</t>
+          <t>6406219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44838</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42505</t>
+          <t>43737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49242</t>
+          <t>49365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80237</t>
+          <t>81261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>460374</t>
+          <t>460575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>485281</t>
+          <t>485555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404962</t>
+          <t>403730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422489</t>
+          <t>422169</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>872442</t>
+          <t>871418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>903437</t>
+          <t>903314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52146</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35523</t>
+          <t>34916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51177</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>81130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400067</t>
+          <t>398515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425700</t>
+          <t>424313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346276</t>
+          <t>346883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362813</t>
+          <t>363173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753537</t>
+          <t>752882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782835</t>
+          <t>782059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69553</t>
+          <t>69428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88120</t>
+          <t>87364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598711</t>
+          <t>598836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654020</t>
+          <t>653635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141937</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154699</t>
+          <t>154855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>747055</t>
+          <t>747811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810253</t>
+          <t>812901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55921</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96602</t>
+          <t>97535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66991</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86973</t>
+          <t>88241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151700</t>
+          <t>150038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>938217</t>
+          <t>937284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>978898</t>
+          <t>978112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910206</t>
+          <t>910463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951771</t>
+          <t>954229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1860316</t>
+          <t>1861978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1925043</t>
+          <t>1923775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51420</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>88838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>79894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121531</t>
+          <t>122674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>432493</t>
+          <t>429400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454734</t>
+          <t>452740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751980</t>
+          <t>750158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>787576</t>
+          <t>786755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1191514</t>
+          <t>1190371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1233519</t>
+          <t>1233151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>39900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67276</t>
+          <t>68229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43516</t>
+          <t>43821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72986</t>
+          <t>74485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226286</t>
+          <t>226687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239276</t>
+          <t>239168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>692876</t>
+          <t>691923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720704</t>
+          <t>720252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>927673</t>
+          <t>926174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957143</t>
+          <t>956838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169644</t>
+          <t>166352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255994</t>
+          <t>254657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202703</t>
+          <t>201705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284359</t>
+          <t>283143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401452</t>
+          <t>398232</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521347</t>
+          <t>521502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3119070</t>
+          <t>3120407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3205420</t>
+          <t>3208712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3288163</t>
+          <t>3289379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3369819</t>
+          <t>3370817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6426239</t>
+          <t>6426084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6546134</t>
+          <t>6549354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>43486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37212</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43352</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>72073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429913</t>
+          <t>430290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452262</t>
+          <t>452521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269468</t>
+          <t>269357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288578</t>
+          <t>288758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>708137</t>
+          <t>708384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737105</t>
+          <t>738005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36183</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40700</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>69320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330751</t>
+          <t>332697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350668</t>
+          <t>352492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331165</t>
+          <t>330937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352357</t>
+          <t>352618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669754</t>
+          <t>669479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698353</t>
+          <t>699348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56554</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28063</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75503</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485835</t>
+          <t>486593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512199</t>
+          <t>511446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139719</t>
+          <t>140019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157181</t>
+          <t>157556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634668</t>
+          <t>631585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665030</t>
+          <t>663778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69739</t>
+          <t>71394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104425</t>
+          <t>105230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115155</t>
+          <t>114832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160656</t>
+          <t>159433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133909</t>
+          <t>1133104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1168595</t>
+          <t>1166940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650432</t>
+          <t>650181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677362</t>
+          <t>676471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1791964</t>
+          <t>1793187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837465</t>
+          <t>1837788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35441</t>
+          <t>35468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44620</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72708</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314096</t>
+          <t>314069</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332136</t>
+          <t>332617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>524132</t>
+          <t>523212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>546992</t>
+          <t>547353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845581</t>
+          <t>844731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875859</t>
+          <t>873558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79730</t>
+          <t>80685</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62062</t>
+          <t>64497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271002</t>
+          <t>272722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287655</t>
+          <t>287856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1169030</t>
+          <t>1168075</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1198623</t>
+          <t>1198928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1448842</t>
+          <t>1446606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1484898</t>
+          <t>1482463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196942</t>
+          <t>197115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255933</t>
+          <t>255430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191521</t>
+          <t>189962</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246866</t>
+          <t>246024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>400404</t>
+          <t>400814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>482527</t>
+          <t>483236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3013239</t>
+          <t>3013742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3072230</t>
+          <t>3072057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3131258</t>
+          <t>3132100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3186603</t>
+          <t>3188162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6164769</t>
+          <t>6164060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6246892</t>
+          <t>6246482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37972</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>57337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>95424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372632</t>
+          <t>370393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400608</t>
+          <t>399901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276482</t>
+          <t>276335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296828</t>
+          <t>296831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>655589</t>
+          <t>656241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692052</t>
+          <t>694328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +3761,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>61442</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>48205</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>80322</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>6,41%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>61442</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>45754</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>79185</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373572</t>
+          <t>373323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397859</t>
+          <t>397173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292276</t>
+          <t>290698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313807</t>
+          <t>313478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +3874,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>690891</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>672011</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>704128</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>93,59%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>690891</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>673148</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>706579</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>89,47%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69724</t>
+          <t>72110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93049</t>
+          <t>94265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>556614</t>
+          <t>554228</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585773</t>
+          <t>583962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226509</t>
+          <t>227518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245549</t>
+          <t>245906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791227</t>
+          <t>790011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825435</t>
+          <t>826527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95033</t>
+          <t>95032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>138723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62548</t>
+          <t>62851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96975</t>
+          <t>96649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167718</t>
+          <t>166644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222799</t>
+          <t>221061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1018551</t>
+          <t>1018592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1062282</t>
+          <t>1062283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669682</t>
+          <t>670008</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>704109</t>
+          <t>703806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1701174</t>
+          <t>1702912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1756255</t>
+          <t>1757329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60944</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68856</t>
+          <t>68522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83276</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119750</t>
+          <t>120060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449652</t>
+          <t>450210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475651</t>
+          <t>475829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688386</t>
+          <t>688720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716046</t>
+          <t>716332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1148089</t>
+          <t>1147779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1184563</t>
+          <t>1184011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67021</t>
+          <t>69217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103102</t>
+          <t>103554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92697</t>
+          <t>93107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136158</t>
+          <t>133809</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226221</t>
+          <t>227381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248001</t>
+          <t>247856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1002154</t>
+          <t>1001702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1038235</t>
+          <t>1036039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1234940</t>
+          <t>1237289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1278401</t>
+          <t>1277991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>285970</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>358663</t>
+          <t>361317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265768</t>
+          <t>262811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>330987</t>
+          <t>328464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>571536</t>
+          <t>565237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>670424</t>
+          <t>667959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3055656</t>
+          <t>3053002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3128349</t>
+          <t>3127694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3205877</t>
+          <t>3208400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3271096</t>
+          <t>3274053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6280759</t>
+          <t>6283224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6379647</t>
+          <t>6385946</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,82 +6018,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>23538</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14863</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33829</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>59642</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>44795</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>76649</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>5,77%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23538</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15384</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35096</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>59642</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>45936</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>77147</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380513</t>
+          <t>379901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404330</t>
+          <t>403524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,82 +6131,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>323517</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>313226</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>332192</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>716505</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>699498</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>731352</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>94,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>323517</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>311959</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>331671</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>716505</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>699000</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>730211</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,82 +6361,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33379</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22694</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>45822</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>61832</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>48578</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>80669</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>10,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33379</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23987</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>46808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>61832</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>47353</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336651</t>
+          <t>337560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358560</t>
+          <t>358810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,82 +6474,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>89,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>338894</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>326451</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>349579</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>687668</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>668831</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>700922</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>89,24%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>338894</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>325465</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>348286</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>687668</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>673703</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>702147</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59355</t>
+          <t>58796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46753</t>
+          <t>46423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77162</t>
+          <t>76779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462559</t>
+          <t>463118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487819</t>
+          <t>488188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140233</t>
+          <t>140863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156783</t>
+          <t>157280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610874</t>
+          <t>611257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641283</t>
+          <t>641613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112492</t>
+          <t>111011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50743</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>79758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130173</t>
+          <t>129982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178671</t>
+          <t>180281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1037146</t>
+          <t>1038627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1075504</t>
+          <t>1076384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743744</t>
+          <t>746118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>775133</t>
+          <t>777080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1796843</t>
+          <t>1795233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1845341</t>
+          <t>1845532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77988</t>
+          <t>76213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86404</t>
+          <t>84718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124986</t>
+          <t>125978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>563481</t>
+          <t>562799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>589605</t>
+          <t>588951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>660256</t>
+          <t>662031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691693</t>
+          <t>692166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1233964</t>
+          <t>1232972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1272546</t>
+          <t>1274232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79755</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121110</t>
+          <t>121414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96512</t>
+          <t>97136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140425</t>
+          <t>139422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258733</t>
+          <t>258679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275871</t>
+          <t>276023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>960915</t>
+          <t>960611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1002270</t>
+          <t>1003322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1228745</t>
+          <t>1229748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1272658</t>
+          <t>1272034</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>231197</t>
+          <t>230651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>294223</t>
+          <t>293182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>264529</t>
+          <t>261890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>327780</t>
+          <t>326952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>511099</t>
+          <t>508294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>604067</t>
+          <t>602082</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3091499</t>
+          <t>3092540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3154525</t>
+          <t>3155071</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3203816</t>
+          <t>3204644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3267067</t>
+          <t>3269706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6313251</t>
+          <t>6315236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6406219</t>
+          <t>6409024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>66050</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>52126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>82895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>475076</t>
+          <t>520020</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>460575</t>
+          <t>503907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>485555</t>
+          <t>529688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>414228</t>
+          <t>452959</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403730</t>
+          <t>443787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422169</t>
+          <t>461783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>889304</t>
+          <t>972979</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871418</t>
+          <t>956134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>903314</t>
+          <t>986903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81130</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413462</t>
+          <t>442421</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398515</t>
+          <t>428022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424313</t>
+          <t>453393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>355564</t>
+          <t>395375</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346883</t>
+          <t>384694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363173</t>
+          <t>402685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>769026</t>
+          <t>837797</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>752882</t>
+          <t>822295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782059</t>
+          <t>854165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381799</t>
+          <t>422378</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381799</t>
+          <t>422378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381799</t>
+          <t>422378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834012</t>
+          <t>905590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834012</t>
+          <t>905590</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834012</t>
+          <t>905590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>32228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>57215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58021</t>
+          <t>63491</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87364</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>627870</t>
+          <t>428665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598836</t>
+          <t>414397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653635</t>
+          <t>439384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149284</t>
+          <t>166953</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142206</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154855</t>
+          <t>172831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>777154</t>
+          <t>595618</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>747811</t>
+          <t>579999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>812901</t>
+          <t>609298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>68039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97535</t>
+          <t>109207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49266</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>66393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122837</t>
+          <t>138743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88241</t>
+          <t>116665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150038</t>
+          <t>164964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>961249</t>
+          <t>1046593</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>937284</t>
+          <t>1022636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>978112</t>
+          <t>1063804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>927931</t>
+          <t>806791</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910463</t>
+          <t>793891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954229</t>
+          <t>817507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1889179</t>
+          <t>1853384</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1861978</t>
+          <t>1827163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923775</t>
+          <t>1875462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44649</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52241</t>
+          <t>66554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88838</t>
+          <t>99073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79894</t>
+          <t>98181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122674</t>
+          <t>138301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>444075</t>
+          <t>532073</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429400</t>
+          <t>517473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452740</t>
+          <t>542401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>767764</t>
+          <t>748780</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>750158</t>
+          <t>731054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>786755</t>
+          <t>763573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1211839</t>
+          <t>1280853</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190371</t>
+          <t>1258802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1233151</t>
+          <t>1298922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68229</t>
+          <t>73659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56526</t>
+          <t>63324</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74485</t>
+          <t>83093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235822</t>
+          <t>230163</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226687</t>
+          <t>218126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239168</t>
+          <t>235103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>708310</t>
+          <t>786734</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>691923</t>
+          <t>769334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720252</t>
+          <t>799341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>944133</t>
+          <t>1016897</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>926174</t>
+          <t>997128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956838</t>
+          <t>1030268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,67 +10691,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>217510</t>
+          <t>241554</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166352</t>
+          <t>211490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>254657</t>
+          <t>280429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>274098</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>246388</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>300973</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>249441</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>201705</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>283143</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>466951</t>
+          <t>515652</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>398232</t>
+          <t>468952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521502</t>
+          <t>559001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -10804,67 +10804,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3157554</t>
+          <t>3199934</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3120407</t>
+          <t>3161059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208712</t>
+          <t>3229998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3357592</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3330717</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3385302</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>92,45%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3323081</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3289379</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3370817</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6480635</t>
+          <t>6557526</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6426084</t>
+          <t>6514177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6549354</t>
+          <t>6604226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572522</t>
+          <t>3631690</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572522</t>
+          <t>3631690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572522</t>
+          <t>3631690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947586</t>
+          <t>7073178</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947586</t>
+          <t>7073178</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947586</t>
+          <t>7073178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
